--- a/output/Data and Chart Outputs/east_med_capacity_monthly_complete.xlsx
+++ b/output/Data and Chart Outputs/east_med_capacity_monthly_complete.xlsx
@@ -2888,7 +2888,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Ember's yearly capacity comes from IRENA / national statistics and is rounded; 'Oil' is Ember's 'Other Fossil', 'Other' is 'Other Renewables'. Ember's Hydro may include pumped storage and its Solar usually includes distributed PV, where an official transmission-network series does not. A held or interpolated value is not an observation.</t>
+          <t>Ember's yearly capacity comes from IRENA / national statistics and is rounded; 'Oil' is Ember's 'Other Fossil', 'Other' is 'Other Renewables'. Ember's Solar can include distributed PV where an official transmission-network series does not, and Ember lists no pumped storage or batteries (blank, NONE). A fuel Ember has no row for (e.g. coal or nuclear in a country without any) is NONE, not zero. A held or interpolated value is not an observation.</t>
         </is>
       </c>
     </row>
@@ -3031,7 +3031,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S6"/>
+  <dimension ref="A1:T6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3130,6 +3130,11 @@
           <t>FILLED</t>
         </is>
       </c>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>NONE main fuels</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -3191,6 +3196,9 @@
       <c r="S2" t="n">
         <v>72.7</v>
       </c>
+      <c r="T2" t="n">
+        <v>11.1</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -3252,6 +3260,9 @@
       <c r="S3" t="n">
         <v>54.5</v>
       </c>
+      <c r="T3" t="n">
+        <v>33.3</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -3313,6 +3324,9 @@
       <c r="S4" t="n">
         <v>63.6</v>
       </c>
+      <c r="T4" t="n">
+        <v>22.2</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -3374,6 +3388,9 @@
       <c r="S5" t="n">
         <v>72.7</v>
       </c>
+      <c r="T5" t="n">
+        <v>11.1</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -3434,6 +3451,9 @@
       </c>
       <c r="S6" t="n">
         <v>72.7</v>
+      </c>
+      <c r="T6" t="n">
+        <v>11.1</v>
       </c>
     </row>
   </sheetData>

--- a/output/Data and Chart Outputs/east_med_capacity_monthly_complete.xlsx
+++ b/output/Data and Chart Outputs/east_med_capacity_monthly_complete.xlsx
@@ -2949,7 +2949,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C4"/>
+  <dimension ref="A1:C6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2977,12 +2977,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>EEHC / MOEE (eehc.gov.eg, moee.gov.eg)</t>
+          <t>EEHC / MOEE (eehc.gov.eg, moee.gov.eg); CAPMAS / MOEE ST_* tables</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>eehc.gov.eg answers a 600-byte stub page with no document links; moee.gov.eg does not resolve from Actions; CAPMAS / MOEE ST_* tables used by EGYPT_GAS.py hold gas and energy balance rows, no installed capacity by fuel</t>
+          <t>eehc.gov.eg answers a ~600-byte stub page with no document links; moee.gov.eg does not resolve from Actions; the CAPMAS / MOEE tables read by EGYPT_GAS.py hold gas and energy balance rows, no installed capacity by fuel</t>
         </is>
       </c>
     </row>
@@ -2999,7 +2999,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>downloads (124 pages); installed capacity by fuel is a chart, one year; earlier-year reports at the same URL pattern return 404</t>
+          <t>downloads (124 pages); installed capacity by fuel (2012-2024) is a stacked-bar chart whose labels come out of the text layer unordered (not safely parseable like the NGA reviews' charts); earlier reports at the same URL pattern return 404; the report's own 24.6 GW (2024) is a cross-check only</t>
         </is>
       </c>
     </row>
@@ -3011,12 +3011,46 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>CERA annual report 2024</t>
+          <t>CERA annual reports 2022 and 2023 (cera.org.cy), TSOC</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>cera.org.cy/.../ektheseis/2024_en.pdf returns 404 (2022 and 2023 exist)</t>
+          <t>2024 report returns 404; the 2022/2023 reports give capacity as PROSE per category (conventional 1,478 -&gt; 1,482.5 MW, wind 157.5 MW, commercial PV 279 -&gt; 358 MW, biomass 9.7 -&gt; 4.2 MW) with net-metered and self-consumption PV as separate cumulative figures (about 100-240 MW) and the series as image charts: no like-for-like multi-year table, so Ember is used</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Jordan</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>NEPCO annual reports (used), MEMR annual reports</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>USED: NEPCO 'Available Capacity of Generating Plants' table, 2020-2024 (2025 only in an Arabic report without it)</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Lebanon</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>EDL / Ministry of Energy and Water</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>not probed (no raw Lebanese feed in the repo); Ember</t>
         </is>
       </c>
     </row>

--- a/output/Data and Chart Outputs/east_med_capacity_monthly_complete.xlsx
+++ b/output/Data and Chart Outputs/east_med_capacity_monthly_complete.xlsx
@@ -177,7 +177,7 @@
             </a:pPr>
             <a:r>
               <a:rPr sz="1200" b="1"/>
-              <a:t>East Med installed capacity, complete monthly series (official annual where reachable, Ember fallback elsewhere) (to Oct/26)</a:t>
+              <a:t>East Med installed capacity, monthly (official annual, Ember fallback) (to Oct/26)</a:t>
             </a:r>
           </a:p>
         </rich>
